--- a/output/pdf_financials_xlsx/ZYUS.xlsx
+++ b/output/pdf_financials_xlsx/ZYUS.xlsx
@@ -495,15 +495,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.206</v>
       </c>
     </row>
     <row r="7">
@@ -512,15 +508,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -529,15 +521,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -546,15 +534,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -563,15 +547,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -580,15 +560,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.206</v>
       </c>
     </row>
     <row r="12">
@@ -597,15 +573,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -614,15 +586,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -631,15 +599,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -648,15 +612,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="16">
@@ -665,15 +625,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-24.657</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-42.591</v>
       </c>
     </row>
     <row r="17">
@@ -682,15 +638,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -733,15 +685,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-24.657</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-42.591</v>
       </c>
     </row>
     <row r="21">
@@ -750,15 +698,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -767,15 +711,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -810,15 +750,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="26">
@@ -827,15 +763,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>38.526562</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>56.040789</v>
       </c>
     </row>
     <row r="27">
@@ -844,15 +776,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-24.657</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-42.591</v>
       </c>
     </row>
     <row r="28">
@@ -861,15 +789,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -878,15 +802,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-24.657</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-42.591</v>
       </c>
     </row>
     <row r="30">
@@ -895,15 +815,11 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-8274.161073825504</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-12134.18803418803</v>
       </c>
     </row>
     <row r="31">
@@ -912,15 +828,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -949,15 +861,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -966,15 +874,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -983,15 +887,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1013,15 +913,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1030,15 +926,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1047,15 +939,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1064,15 +952,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="42">
@@ -1081,15 +965,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1098,15 +978,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1115,15 +991,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1132,15 +1004,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1149,15 +1017,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1166,15 +1030,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1183,15 +1043,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1217,15 +1073,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1234,15 +1086,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1251,15 +1099,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1268,15 +1112,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1285,15 +1125,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1319,15 +1155,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1336,15 +1168,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1379,15 +1207,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1396,15 +1220,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1443,15 +1263,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1460,15 +1276,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1477,15 +1289,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1494,15 +1302,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1511,15 +1315,11 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1528,15 +1328,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1545,15 +1341,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1562,15 +1354,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1579,15 +1367,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1596,15 +1380,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1613,15 +1393,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1630,15 +1406,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1664,15 +1436,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1681,15 +1449,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1698,15 +1462,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1732,15 +1492,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1749,15 +1505,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1766,15 +1518,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1783,15 +1531,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1800,15 +1544,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1847,15 +1587,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>2.673</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -1864,15 +1600,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1894,15 +1626,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="92">
@@ -1911,15 +1639,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1928,15 +1652,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1945,15 +1665,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>-5.259</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="95">
@@ -1962,15 +1678,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1979,15 +1691,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>-5.259</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="97">
@@ -1996,15 +1704,11 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>-1.116086587436333</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="98">
@@ -2020,15 +1724,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-24.657</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-42.591</v>
       </c>
     </row>
     <row r="100">
@@ -2037,15 +1737,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2067,15 +1763,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2084,15 +1776,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2101,15 +1789,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2118,15 +1802,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2135,15 +1815,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="107">
@@ -2152,15 +1828,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2169,15 +1841,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2186,15 +1854,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2203,15 +1867,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2233,15 +1893,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2250,15 +1906,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2267,15 +1919,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2284,15 +1932,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2301,15 +1945,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2318,15 +1958,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2335,15 +1971,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2369,15 +2001,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2386,15 +2014,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2403,15 +2027,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2420,15 +2040,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2437,15 +2053,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2454,15 +2066,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2471,15 +2079,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2505,15 +2109,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2552,15 +2152,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2569,15 +2165,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-9.574</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-18.012</v>
       </c>
     </row>
     <row r="133">
@@ -2586,15 +2178,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>-8.824</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>-18</v>
       </c>
     </row>
     <row r="134">
@@ -2603,15 +2191,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>-0.281</v>
       </c>
     </row>
     <row r="135">
@@ -2620,15 +2204,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-10.134</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-18.293</v>
       </c>
     </row>
   </sheetData>
@@ -2642,7 +2222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2908,7 +2488,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1 3,244</t>
+          <t>Loans and borrowings 15 6 ,149 899 total</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3069,7 +2649,11 @@
           <t>Accumulated other comprehensive income (loss) 1 2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.012</v>
       </c>
@@ -3121,7 +2705,11 @@
           <t>Net loss $</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>-24.657</v>
       </c>
@@ -4001,7 +3589,11 @@
           <t>Other expenses 19 3 52</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.065</v>
       </c>
@@ -4022,7 +3614,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4 2,312</t>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045 total</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -4073,7 +3665,11 @@
           <t>Foreign exchange loss 8 1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.003</v>
       </c>
@@ -4207,6 +3803,126 @@
       </c>
       <c r="F61" s="5" t="n">
         <v>56122.095</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Interest expense (loans and borrowings) $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>3.047</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1.919</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Interest expense (leases)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Accretion</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>1.042</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>20. Finance Costs total</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>5.464</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>3.845</v>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/ZYUS.xlsx
+++ b/output/pdf_financials_xlsx/ZYUS.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZYUS.xlsx
+++ b/output/pdf_financials_xlsx/ZYUS.xlsx
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.197</v>
+        <v>-0.232</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.206</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="7">
@@ -527,10 +527,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>2.208</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1.309</v>
       </c>
     </row>
     <row r="9">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>18.56</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>42.312</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.197</v>
+        <v>-18.792</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.206</v>
+        <v>-42.141</v>
       </c>
     </row>
     <row r="12">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-24.657</v>
+        <v>-24.715</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-42.591</v>
+        <v>-48.439</v>
       </c>
     </row>
     <row r="17">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>5.848</v>
       </c>
     </row>
     <row r="18">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-24.657</v>
+        <v>-24.715</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-42.591</v>
+        <v>-48.439</v>
       </c>
     </row>
     <row r="28">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>4.045</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>3.106</v>
       </c>
     </row>
     <row r="29">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-24.657</v>
+        <v>-20.67</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-42.591</v>
+        <v>-45.333</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-8274.161073825504</v>
+        <v>-6936.241610738254</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-12134.18803418803</v>
+        <v>-12915.38461538462</v>
       </c>
     </row>
     <row r="31">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2346752984017803</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-12.07291645161956</v>
       </c>
     </row>
     <row r="32">
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>1.874</v>
       </c>
     </row>
     <row r="36">
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.874</v>
       </c>
     </row>
     <row r="37">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>0</v>
+        <v>4.202</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0</v>
+        <v>2.042</v>
       </c>
     </row>
     <row r="48">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>2.021</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="49">
@@ -1061,15 +1061,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>6.266</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>9.388</v>
       </c>
     </row>
     <row r="50">
@@ -1213,10 +1209,10 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>0</v>
+        <v>5.871</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0</v>
+        <v>5.871</v>
       </c>
     </row>
     <row r="61">
@@ -1238,15 +1234,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>-1.554</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>-9.382</v>
       </c>
     </row>
     <row r="63">
@@ -1321,10 +1313,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>13.038</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>6.691</v>
       </c>
     </row>
     <row r="69">
@@ -1412,10 +1404,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0</v>
+        <v>6.553</v>
       </c>
     </row>
     <row r="76">
@@ -1424,15 +1416,11 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>14.268</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>13.244</v>
       </c>
     </row>
     <row r="77">
@@ -1524,10 +1512,10 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>0</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>0</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="84">
@@ -1537,10 +1525,10 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>0</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>0</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="85">
@@ -1562,15 +1550,11 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>-4.297</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>-13.239</v>
       </c>
     </row>
     <row r="87">
@@ -1645,10 +1629,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.629</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.393</v>
       </c>
     </row>
     <row r="93">
@@ -1671,10 +1655,10 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>-5.259</v>
+        <v>4.741</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.001</v>
+        <v>23.114</v>
       </c>
     </row>
     <row r="95">
@@ -1697,10 +1681,10 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>-5.259</v>
+        <v>4.741</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.001</v>
+        <v>23.114</v>
       </c>
     </row>
     <row r="97">
@@ -1710,10 +1694,10 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>-1.116086587436333</v>
+        <v>1.006154499151104</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>3852.333333333333</v>
       </c>
     </row>
     <row r="98">
@@ -1743,10 +1727,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4.045</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>3.106</v>
       </c>
     </row>
     <row r="101">
@@ -1769,10 +1753,10 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="103">
@@ -1795,10 +1779,10 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>0</v>
+        <v>2.336</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0</v>
+        <v>-5.118</v>
       </c>
     </row>
     <row r="105">
@@ -1821,10 +1805,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.005</v>
+        <v>2.791</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.001</v>
+        <v>-5.138</v>
       </c>
     </row>
     <row r="107">
@@ -1989,15 +1973,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.592</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>4.64</v>
       </c>
     </row>
     <row r="120">
@@ -2127,15 +2107,11 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>9.628</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>17.138</v>
       </c>
     </row>
     <row r="130">
@@ -2171,10 +2147,10 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>-9.574</v>
+        <v>-0.538</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>-18.012</v>
+        <v>3.766</v>
       </c>
     </row>
     <row r="133">
@@ -2184,10 +2160,10 @@
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>-8.824</v>
+        <v>0.212</v>
       </c>
       <c r="C133" s="3" t="n">
-        <v>-18</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="134">
@@ -2227,7 +2203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2697,482 +2673,508 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-24.657</v>
+        <v>0.212</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-42.591</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 3 ,106 4 ,045</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inventory write-off</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="5" t="n">
-        <v>0.429</v>
+          <t>Short-term investments</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>2.181</v>
+        <v>1.874</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 3 ,106 4 ,045</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Asset impairment</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts receivable 7</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.243</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.57</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 3 ,106 4 ,045</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Impairment of intangible asset 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Inventory 8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
-        <v>2.091</v>
+        <v>4.202</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2.198</v>
+        <v>2.042</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 3 ,106 4 ,045</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Derivative loss 15 1 ,115</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Prepaid expenses and other assets 9</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OtherAssets</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
-        <v>0.061</v>
+        <v>1.609</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.006</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Listing expense 2 1 ,958 -</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Interest paid</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Current assets total</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>-0.114</v>
+        <v>6.266</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.226</v>
+        <v>9.388</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Listing expense 2 1 ,958 -</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unrealized Foreign exchange gain (loss) 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Property, plant and equipment 10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>-0.017</v>
+        <v>14.435</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.008</v>
+        <v>11.481</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Listing expense 2 1 ,958 -</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Share-based compensation expense 2 66</t>
+          <t>Right-of-use leased assets 11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>2.597</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.001</v>
+        <v>2.413</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Listing expense 2 1 ,958 -</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Intangible assets 12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>-0.058</v>
+        <v>35.387</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-5.848</v>
+        <v>12.322</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Listing expense 2 1 ,958 -</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other adjustment 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Goodwill 13</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>-0.146</v>
+        <v>5.871</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.09</v>
+        <v>5.871</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Short-term investments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other assets 9</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OtherAssets</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.156</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accounts receivable (347)</t>
+          <t>Total assets $</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.005</v>
+        <v>64.712</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.001</v>
+        <v>41.627</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inventory (21)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 14 $</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>0.05</v>
+        <v>13.038</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.004</v>
+        <v>6.691</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prepaid expenses and other assets 7</t>
+          <t>Loans and borrowings 15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>-0.272</v>
+        <v>0.899</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.036</v>
+        <v>6.149</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (5,118) 2 ,336</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Lease obligations 11</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
-        <v>-9.574</v>
+        <v>0.331</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-18.012</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Acquisition of property, plant and equipment</t>
+          <t>Current liabilities total</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>14.268</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.281</v>
+        <v>13.244</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Proceeds from 2023 promissory notes, net 15 5</t>
+          <t>Lease obligations 11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" s="5" t="n">
+        <v>2.875</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Proceeds from concurrent financing, net 16 1</t>
+          <t>Loans and borrowings 15</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="5" t="n">
+        <v>30.799</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>8.443</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>Derivative liabilities 15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>0.175</v>
+        <v>3.976</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3183,229 +3185,249 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Proceeds from revolver 15 3 50</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Deferred tax liability 22</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NonCurrentDeferredTaxesLiabilities</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
-        <v>0.04</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.008</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Proceeds from short-term loan 15 -</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>59.971</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.002</v>
+        <v>18.513</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Repayment of short-term loans 15</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital 16</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>92.673</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-0.2</v>
+        <v>154.088</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Repayment of shareholder loan 15</t>
+          <t>Warrants 17</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="5" t="n">
+        <v>3.423</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-2</v>
+        <v>3.808</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Repayment of revolver 15</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Contributed surplus</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
-        <v>-0.1</v>
+        <v>5.629</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-1.09</v>
+        <v>5.393</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Repayment of promissory notes 15</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>-97.596</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.349</v>
+        <v>-140.187</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Repayment of term loan 15</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accumulated other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.612</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lease payments</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Total shareholders' equity</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
-        <v>-0.243</v>
+        <v>4.741</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.464</v>
+        <v>23.114</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash 3 ,766 (538)</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 2</t>
+          <t>Total liabilities and shareholders' equity $</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.75</v>
+        <v>64.712</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.012</v>
+        <v>41.627</v>
       </c>
     </row>
     <row r="46">
@@ -3416,517 +3438,2705 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash 3 ,766 (538)</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cash, end of year $ 3 ,978 $</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>0.012</v>
+        <v>-24.657</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.002</v>
+        <v>-42.591</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 3 ,106 4 ,045</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sales $</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Inventory write-off</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>0.298</v>
+        <v>0.429</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.351</v>
+        <v>2.181</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 3 ,106 4 ,045</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.101</v>
+          <t>Asset impairment</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.145</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+          <t>Depreciation and amortization 3 ,106 4 ,045</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Provision for inventory impairment 8 2 ,181</t>
+          <t>Impairment of intangible asset 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>0.006</v>
+        <v>2.091</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.004</v>
+        <v>2.198</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+          <t>Depreciation and amortization 3 ,106 4 ,045</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Asset impairment 10 5</t>
+          <t>Derivative loss 15 1 ,115</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="5" t="n">
+        <v>0.061</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+          <t>Listing expense 2 1 ,958 -</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Share-based compensation 21 2 66</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.114</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+          <t>Listing expense 2 1 ,958 -</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medical education, branding and marketing 3 24</t>
+          <t>Unrealized Foreign exchange gain (loss) 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>0.053</v>
+        <v>-0.017</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+          <t>Listing expense 2 1 ,958 -</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Other expenses 19 3 52</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation expense 2 66</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>0.065</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+          <t>Listing expense 2 1 ,958 -</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045 total</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>8.56</v>
+        <v>-0.058</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.001</v>
+        <v>-5.848</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Finance costs 20 3 ,845 5 ,464</t>
+          <t>Listing expense 2 1 ,958 -</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Derivative loss 24 1 ,115</t>
+          <t>Other adjustment 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0.061</v>
+        <v>-0.146</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.006</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Finance costs 20 3 ,845 5 ,464</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Foreign exchange loss 8 1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>0.003</v>
+          <t>Short-term investments</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Income tax</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 22</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Accounts receivable (347)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
-        <v>0.058</v>
+        <v>0.005</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>5.848</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Income tax</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Inventory (21)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>-24.657</v>
+        <v>0.05</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-42.591</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) gain ( 600) 1 ,701</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Comprehensive (loss) $</t>
+          <t>Prepaid expenses and other assets 7</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>-22.956</v>
+        <v>-0.272</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-43.191</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Accounts payable and accrued liabilities (5,118) 2 ,336</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Basic and diluted 23 $</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-6.4e-07</v>
+        <v>-9.574</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-7.6e-07</v>
+        <v>-18.012</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Weighted average number of shares</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Basic and diluted 23</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Acquisition of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
-        <v>38486.396</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>56122.095</v>
+        <v>-0.281</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20. Finance Costs</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Interest expense (loans and borrowings) $</t>
+          <t>Proceeds from 2023 promissory notes, net 15 5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>3.047</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>1.919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20. Finance Costs</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Interest expense (leases)</t>
+          <t>Proceeds from concurrent financing, net 16 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>0.341</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.311</v>
+        <v>8.443</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20. Finance Costs</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Accretion</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Proceeds from issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>1.042</v>
+        <v>0.175</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20. Finance Costs</t>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Proceeds from revolver 15 3 50</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>0.221</v>
+        <v>0.04</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.573</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20. Finance Costs</t>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>20. Finance Costs total</t>
+          <t>Proceeds from short-term loan 15 -</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Repayment of short-term loans 15</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Repayment of shareholder loan 15</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Repayment of revolver 15</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Repayment of promissory notes 15</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>-0.349</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Repayment of term loan 15</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.002</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Proceeds from shareholder loan, net - 2 ,000</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lease payments</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-0.464</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in cash 3 ,766 (538)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Cash, beginning of year 2</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in cash 3 ,766 (538)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cash, end of year $ 3 ,978 $</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>3.106</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Inventory write-off</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>2.181</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Asset impairment</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Impairment of intangible asset</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>22.198</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Derivative loss 15</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1.115</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Finance costs 20</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
         <v>5.464</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F80" s="5" t="n">
+        <v>3.845</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Listing expense 2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>1.958</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.114</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-0.226</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Unrealized Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Share-based compensation expense</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-5.848</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Other adjustment</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>-0.146</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-0.347</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.021</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Prepaid expenses and other assets</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>-0.272</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.736</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-5.118</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Changes in operating assets and liabilities</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>-9.574</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>-18.012</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Acquisition of Phoenix Canada Oil Company Limited, net of cash &amp; cash equivalents 2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>4.921</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Net cash provided (used) in investing activities</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>-0.592</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Proceeds from convertible promissory notes, net 15</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Proceeds from 2023 promissory notes, net 15</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Proceeds from concurrent financing, net 16</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>18.443</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Proceeds from unit offering, net 15</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>6.706</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Proceeds from shareholder loan, net</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Proceeds from revolver 15</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Proceeds from short-term loan 15</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Repayment of short-term loans 15</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Repayment of shareholder loan 15</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Repayment of revolver 15</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Repayment of promissory notes 15</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-0.349</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Repayment of term loan 15</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>-0.002</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Lease payments</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>-0.464</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>9.628</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>17.138</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Net increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-0.538</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>3.766</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>0.212</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>3.978</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Sales $</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.145</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Provision for inventory impairment 8 2 ,181</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Asset impairment 10 5</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Share-based compensation 21 2 66</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Medical education, branding and marketing 3 24</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Other expenses 19 3 52</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12 3 ,106 4 ,045 total</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Finance costs 20 3 ,845 5 ,464</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Derivative loss 24 1 ,115</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Finance costs 20 3 ,845 5 ,464</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss 8 1</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery 22</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" s="5" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>5.848</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>-24.657</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>-42.591</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Other comprehensive (loss) gain ( 600) 1 ,701</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Comprehensive (loss) $</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>-22.956</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>-43.191</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Net loss per share</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Basic and diluted 23 $</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>-6.4e-07</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>-7.6e-07</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Basic and diluted 23</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
+        <v>38486.396</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>56122.095</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Inventory write-off 8</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" s="5" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>-0.035</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gross profit (loss)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>0.171</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>General and administrative 18 $</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>8.683</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>12.006</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Research and development</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>1.309</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 10,11,12</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>4.045</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>3.106</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Provision for inventory impairment 8</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>2.181</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Asset impairment 10</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Share-based compensation 21</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" s="5" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>0.266</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Medical education, branding and marketing</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" s="5" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>0.324</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Impairment of intangible asset 12</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>22.198</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Other expenses 19</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>42.312</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>-18.792</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-42.141</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Listing expense 2</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>1.958</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Investment and other income</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.215</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.701</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Finance costs 20</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
+        <v>5.464</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>3.845</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Derivative loss 24</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>1.115</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.081</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Loss before income tax</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>-24.715</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>-48.439</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Other comprehensive (loss) gain</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" s="5" t="n">
+        <v>1.701</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Comprehensive (loss) $</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" s="5" t="n">
+        <v>-22.956</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>-43.191</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Interest expense (loans and borrowings) $</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" s="5" t="n">
+        <v>3.047</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>1.919</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Interest expense (leases)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" s="5" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Accretion</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" s="5" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>1.042</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" s="5" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>0.573</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>20. Finance Costs</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>20. Finance Costs total</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" s="5" t="n">
+        <v>5.464</v>
+      </c>
+      <c r="F151" s="5" t="n">
         <v>3.845</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/ZYUS.xlsx
+++ b/output/pdf_financials_xlsx/ZYUS.xlsx
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.978</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.874</v>
+        <v>5.852</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.021</v>
+        <v>1.809</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.47</v>
+        <v>1.492</v>
       </c>
     </row>
     <row r="49">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.464</v>
       </c>
     </row>
     <row r="125">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.464</v>
       </c>
     </row>
     <row r="126">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
@@ -4112,7 +4112,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>-0.243</v>
       </c>
@@ -4982,7 +4986,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="n">
         <v>-0.243</v>
       </c>

--- a/output/pdf_financials_xlsx/ZYUS.xlsx
+++ b/output/pdf_financials_xlsx/ZYUS.xlsx
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.058</v>
+        <v>-0.058</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5.848</v>
+        <v>-5.848</v>
       </c>
     </row>
     <row r="18">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="71">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="72">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>1.23</v>
+        <v>0.899</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>6.553</v>
+        <v>6.149</v>
       </c>
     </row>
     <row r="76">
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="79">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="80">
@@ -1468,15 +1468,11 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.6762286437460452</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.1306567448299732</v>
       </c>
     </row>
     <row r="81">
@@ -1818,10 +1814,10 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="108">
@@ -3072,7 +3068,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.331</v>
       </c>
@@ -3124,7 +3124,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>2.875</v>
       </c>
@@ -3624,7 +3628,11 @@
           <t>Share-based compensation expense 2 66</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.008999999999999999</v>
       </c>
@@ -3648,7 +3656,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>-0.058</v>
       </c>
@@ -4420,7 +4432,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.109</v>
       </c>
@@ -4444,7 +4460,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>-0.058</v>
       </c>
@@ -5376,7 +5396,11 @@
           <t>Deferred income tax recovery 22</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E121" s="5" t="n">
         <v>0.058</v>
       </c>
